--- a/Anumoy_Pathak_RedBus/RTM_Bus_Seat_Booking.xlsx
+++ b/Anumoy_Pathak_RedBus/RTM_Bus_Seat_Booking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d6a5426fd29e00d/Desktop/Anumoy_Pathak_RedBus/Anumoy_Pathak_RedBus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{017628E4-399E-49BC-A658-0B9CB6DD37F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC870F72-269F-4725-ACAF-0CC17B653DA9}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{017628E4-399E-49BC-A658-0B9CB6DD37F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A09702-06FC-4EAA-937B-690B303F4ECE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -378,10 +378,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
